--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260827.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260827.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>913,037,000</t>
+          <t>177,011,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.49%</t>
+          <t>9.55%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>177,011,000</t>
+          <t>913,037,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.47%</t>
+          <t>9.42%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.11%</t>
+          <t>6.14%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.07%</t>
+          <t>6.08%</t>
         </is>
       </c>
     </row>
@@ -704,51 +704,51 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>4.10%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>187,201,000</t>
+          <t>602,716,270</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.64%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>602,716,270</t>
+          <t>187,201,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.64%</t>
+          <t>3.59%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.16%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
@@ -836,73 +836,73 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>202609TX</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>456,296,250</t>
+          <t>1,963</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.92%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>31,356,000</t>
+          <t>456,296,250</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.90%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>202609TX</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>1,873</t>
+          <t>31,356,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.78%</t>
         </is>
       </c>
     </row>
@@ -924,51 +924,51 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>199,761,000</t>
+          <t>26,219,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>26,219,000</t>
+          <t>199,761,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
@@ -990,46 +990,46 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>83,020,000</t>
+          <t>236,458,056</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>98,298,442</t>
+          <t>83,020,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,22 +1041,22 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>236,458,056</t>
+          <t>98,298,442</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.40%</t>
         </is>
       </c>
     </row>
@@ -1078,51 +1078,51 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.38%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>99,033,000</t>
+          <t>28,901,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.23%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>28,901,000</t>
+          <t>99,033,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
@@ -1271,29 +1271,29 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>8,886,000</t>
+          <t>7,686,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>B618CW</t>
+          <t>A97102</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>P11台積1B</t>
+          <t>97央債甲2</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1301,17 +1301,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>B95553</t>
+          <t>B618CW</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>P08凱控1B</t>
+          <t>P11台積1B</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1319,17 +1319,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>B95555</t>
+          <t>B95552</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>P09凱控1B</t>
+          <t>P08凱控1A</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>85,000,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
@@ -1337,17 +1337,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>B96525</t>
+          <t>B95553</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>P11元金2</t>
+          <t>P08凱控1B</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>120,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr"/>
@@ -1355,17 +1355,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>B95555</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>P09凱控1B</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>30,469,363,379</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr"/>
@@ -1373,17 +1373,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>B96525</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>P11元金2</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>5,122,924,661</t>
+          <t>120,000,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr"/>
@@ -1391,20 +1391,74 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
+          <t>B97872</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>P13富邦金1</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>45,000,000</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>31,076,949,698</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>M_NTD</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>MARGIN</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>5,145,089,626</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
           <t>PFUR_NTD</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>PAYABLES FOR UNITS REDEEMED</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr"/>
+      <c r="D61" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
